--- a/public/templates/LaporanKekerasanAnak.xlsx
+++ b/public/templates/LaporanKekerasanAnak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89B87CA3-3C8F-4F7A-A693-01F48850EB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D244F33-139A-4461-88B0-3EC261CC2F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{915D8BA5-8586-4647-B282-2A3D32D5202A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{915D8BA5-8586-4647-B282-2A3D32D5202A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -168,19 +166,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -188,8 +186,8 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -528,251 +526,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A29045B-F50D-4F52-8830-C66A5A3472AE}">
   <dimension ref="B4:R13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="4" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="4">
-        <v>2021</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4">
-        <v>2022</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+    <row r="5" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2">
+        <v>2025</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="4" t="s">
+    <row r="6" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="7"/>
-    </row>
-    <row r="8" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="7"/>
-    </row>
-    <row r="9" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="7"/>
-    </row>
-    <row r="10" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="5"/>
+    </row>
+    <row r="10" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="7"/>
-    </row>
-    <row r="11" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="5"/>
+    </row>
+    <row r="11" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="7"/>
-    </row>
-    <row r="12" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="5"/>
+    </row>
+    <row r="12" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="7"/>
-    </row>
-    <row r="13" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>7</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="C4:J6"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C10:J10"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="Q13:R13"/>
@@ -789,29 +805,11 @@
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="C4:J6"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K4:R4"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="M9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
